--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1315-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1315-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4136499E-028F-4C58-B6AF-6CC5DD7DA92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E20AA9D-5C33-4FE0-B816-4527A392CF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{DE7C6731-592F-4E56-AD23-E850B3D014AC}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{40B3E79A-44F2-4267-843C-FE645DF61179}"/>
   </bookViews>
   <sheets>
     <sheet name="1315-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1541,28 +1541,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0701F2D1-CC95-4B40-B850-F0AA52097041}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065C4B70-29F4-4233-97EB-6E76AA544E0C}">
   <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1596,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1752,7 +1752,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2410,7 +2410,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2021</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2020</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>9.98</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2019</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2018</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2017</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2016</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2015</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2014</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2013</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2012</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2011</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2010</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2009</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2008</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2007</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2006</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2005</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2004</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2003</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2002</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>2001</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2000</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>1999</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>1998</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>1997</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>1996</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>1995</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>1994</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <v>1993</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>1992</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
         <v>1991</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="37">
         <v>1990</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
         <v>1989</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="37">
         <v>1988</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="35">
         <v>1986</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="37" t="s">
         <v>68</v>
       </c>
